--- a/Experiment/September set/onderzoek_meta_alle_machines.xlsx
+++ b/Experiment/September set/onderzoek_meta_alle_machines.xlsx
@@ -1,34 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f2810a0d4408f349/Documenten/GitHub/OR5/Experiment/September set/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="25" documentId="11_2B5986375229464C1D03C5F05082D0B156EFFBC3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F120677-1AA8-41BC-B002-83CFEC768127}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Alle machines" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Alle machines" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+  <si>
+    <t>Snelheidsverhoging (%)</t>
+  </si>
+  <si>
+    <t>M1 (%)</t>
+  </si>
+  <si>
+    <t>M2 (%)</t>
+  </si>
+  <si>
+    <t>M3 (%)</t>
+  </si>
+  <si>
+    <t>Penalty SA</t>
+  </si>
+  <si>
+    <t>Penalty SA Improved</t>
+  </si>
+  <si>
+    <t>Rekentijd SA (s)</t>
+  </si>
+  <si>
+    <t>Rekentijd Improving (s)</t>
+  </si>
+  <si>
+    <t>Totale rekentijd (s)</t>
+  </si>
+  <si>
+    <t>Verbetering SA (%)</t>
+  </si>
+  <si>
+    <t>Verbetering Improved (%)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,82 +88,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34F408EE-2509-4C77-ABDF-AA3A68AC5363}" name="Table1" displayName="Table1" ref="B11:F17" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="B11:F17" xr:uid="{34F408EE-2509-4C77-ABDF-AA3A68AC5363}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{C453834B-3A0F-4E71-B8E2-CB2B52E630CC}" name="M1 (%)"/>
+    <tableColumn id="2" xr3:uid="{470558FA-F941-4613-949C-CF9036A8ACC2}" name="M2 (%)"/>
+    <tableColumn id="3" xr3:uid="{314D3F3D-A64E-4FEC-BEBF-35B7BBF2421D}" name="M3 (%)"/>
+    <tableColumn id="4" xr3:uid="{EE5AFC4B-0422-4A4D-86E6-8FF740FA43A4}" name="Penalty SA Improved"/>
+    <tableColumn id="5" xr3:uid="{5609A8F1-0FC6-4062-9460-08A1CB114803}" name="Rekentijd SA (s)"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,282 +430,388 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="4" width="8.7265625" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Snelheidsverhoging (%)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>M1 (%)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>M2 (%)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>M3 (%)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Penalty SA</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Penalty SA Improved</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Rekentijd SA (s)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Rekentijd Improving (s)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Totale rekentijd (s)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Verbetering SA (%)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Verbetering Improved (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2">
         <v>25</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>25</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>25</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>25</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>6</v>
       </c>
-      <c r="G2" t="n">
-        <v>35.44137240000055</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0184835000000021</v>
-      </c>
-      <c r="I2" t="n">
-        <v>35.45985590000055</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="G2">
+        <v>35.441372400000553</v>
+      </c>
+      <c r="H2">
+        <v>1.8483500000002099E-2</v>
+      </c>
+      <c r="I2">
+        <v>35.459855900000548</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>26</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>26</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>26</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>26</v>
       </c>
-      <c r="E3" t="n">
-        <v>8.326278659611972</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8.326278659611972</v>
-      </c>
-      <c r="G3" t="n">
-        <v>35.27929769999901</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.01794929999960004</v>
-      </c>
-      <c r="I3" t="n">
-        <v>35.29724699999861</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-38.77131099353288</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-38.77131099353288</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="E3">
+        <v>8.3262786596119724</v>
+      </c>
+      <c r="F3">
+        <v>8.3262786596119724</v>
+      </c>
+      <c r="G3">
+        <v>35.279297699999013</v>
+      </c>
+      <c r="H3">
+        <v>1.794929999960004E-2</v>
+      </c>
+      <c r="I3">
+        <v>35.297246999998613</v>
+      </c>
+      <c r="J3">
+        <v>-38.771310993532879</v>
+      </c>
+      <c r="K3">
+        <v>-38.771310993532879</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4">
         <v>27</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>27</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>27</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>27</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>9.268591426071751</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>9.268591426071751</v>
       </c>
-      <c r="G4" t="n">
-        <v>35.46049299999868</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.01831209999727434</v>
-      </c>
-      <c r="I4" t="n">
-        <v>35.47880509999595</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-54.47652376786252</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-54.47652376786252</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="G4">
+        <v>35.460492999998678</v>
+      </c>
+      <c r="H4">
+        <v>1.8312099997274341E-2</v>
+      </c>
+      <c r="I4">
+        <v>35.478805099995952</v>
+      </c>
+      <c r="J4">
+        <v>-54.476523767862517</v>
+      </c>
+      <c r="K4">
+        <v>-54.476523767862517</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5">
         <v>28</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>28</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>28</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>28</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>35.57480009999927</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>35.57480009999927</v>
-      </c>
-      <c r="J5" t="n">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>35.574800099999273</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>35.574800099999273</v>
+      </c>
+      <c r="J5">
         <v>100</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>100</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6">
         <v>29</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>29</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>29</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>29</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>35.47212800000125</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>35.47212800000125</v>
-      </c>
-      <c r="J6" t="n">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>35.472128000001248</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>35.472128000001248</v>
+      </c>
+      <c r="J6">
         <v>100</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>100</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7">
         <v>30</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>30</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>30</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>30</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>35.9180137000003</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>35.9180137000003</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>35.918013700000301</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>35.918013700000301</v>
+      </c>
+      <c r="J7">
         <v>100</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
+        <v>25</v>
+      </c>
+      <c r="C12" s="1">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2">
+        <v>6</v>
+      </c>
+      <c r="F12" s="2">
+        <v>35.441372400000553</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1">
+        <v>26</v>
+      </c>
+      <c r="D13" s="1">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8.3262786596119724</v>
+      </c>
+      <c r="F13" s="2">
+        <v>35.279297699999013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B14" s="1">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1">
+        <v>27</v>
+      </c>
+      <c r="D14" s="1">
+        <v>27</v>
+      </c>
+      <c r="E14" s="2">
+        <v>9.268591426071751</v>
+      </c>
+      <c r="F14" s="2">
+        <v>35.460492999998678</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B15" s="1">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>28</v>
+      </c>
+      <c r="D15" s="1">
+        <v>28</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>35.574800099999273</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B16" s="1">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1">
+        <v>29</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2">
+        <v>35.472128000001248</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B17" s="1">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1">
+        <v>30</v>
+      </c>
+      <c r="D17" s="1">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>35.918013700000301</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>